--- a/data/documents.xlsx
+++ b/data/documents.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,15 +466,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>uf</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>excerpt</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>full_text</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>highlight</t>
         </is>
@@ -518,15 +523,20 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>UF Cardiologie</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>Patiente admise pour décompensation cardiaque globale sur cardiopathie ischémique connue, avec insuffisance rénale aiguë sur chronique stade IIIB. Évolution favorable sous traitement diurétique IV.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Patiente admise pour décompensation cardiaque globale sur cardiopathie ischémique connue, avec insuffisance rénale aiguë sur chronique stade IIIB. Évolution favorable sous traitement diurétique IV. Le bilan biologique d'entrée retrouvait un NT-proBNP à 5400 ng/L et une créatininémie à 142 µmol/L. L'échocardiographie a confirmé une dysfonction ventriculaire gauche sévère (FEVG 30%). Traitement diurétique intraveineux avec surveillance stricte de la diurèse, permettant une amélioration clinique et biologique progressive. Sortie à domicile avec majoration du traitement de fond et mise en place d'une hospitalisation à domicile (HAD).</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>cardiopathie ischémique</t>
         </is>
@@ -570,15 +580,20 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>UF Imagerie cardiaque</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>FEVG estimée à 30%, hypokinésie globale. Pas d'épanchement péricardique. Valves sans anomalie significative.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>FEVG estimée à 30%, hypokinésie globale. Pas d'épanchement péricardique. Valves sans anomalie significative. Cinétique globale altérée de façon homogène, sans anomalie segmentaire focale évocatrice d'une séquelle territoriale univoque. Fonction diastolique non évaluable de façon fiable dans ce contexte.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>FEVG estimée à 30%</t>
         </is>
@@ -622,15 +637,20 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>UF Cardiologie</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Poids stable à 68kg, auscultation pulmonaire libre. Poursuite du traitement, kaliémie basse à surveiller.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Poids stable à 68kg, auscultation pulmonaire libre. Poursuite du traitement, kaliémie basse à surveiller. Le traitement bêta-bloquant et l'IEC ont été maintenus à dose stable. Surveillance rapprochée du ionogramme prévue en ville dans les 15 jours compte tenu de la kaliémie basse.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>kaliémie basse</t>
         </is>
@@ -674,15 +694,20 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>UF Cardiologie interventionnelle</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Sténose serrée de l'artère interventriculaire antérieure proximale, traitée par angioplastie et pose d'un stent actif.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Sténose serrée de l'artère interventriculaire antérieure proximale, traitée par angioplastie et pose d'un stent actif. Angioplastie réalisée avec succès par voie radiale droite, sans complication au point de ponction. Double antiagrégation plaquettaire instaurée pour une durée de 12 mois.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>stent actif</t>
         </is>
@@ -726,15 +751,20 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>UF Pneumologie</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Pneumopathie basale droite d'allure bactérienne, syndrome inflammatoire biologique marqué à l'entrée. Évolution favorable sous antibiothérapie.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Pneumopathie basale droite d'allure bactérienne, syndrome inflammatoire biologique marqué à l'entrée. Évolution favorable sous antibiothérapie. Hémocultures négatives, antigénurie légionelle et pneumocoque négatives. Antibiothérapie probabiliste par amoxicilline-acide clavulanique avec relais oral à J5, bonne évolution clinique et biologique.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Pneumopathie basale droite</t>
         </is>
@@ -778,15 +808,20 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>UF Imagerie</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>Foyer de condensation alvéolaire du lobe inférieur droit, sans épanchement pleural associé.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Foyer de condensation alvéolaire du lobe inférieur droit, sans épanchement pleural associé. Contrôle radiologique de sortie non réalisé, à prévoir à distance si persistance de symptômes.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>foyer de condensation alvéolaire</t>
         </is>
@@ -830,15 +865,20 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>UF Pneumologie</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>Pneumopathie basale gauche, évolution favorable sous antibiothérapie orale.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Pneumopathie basale gauche, évolution favorable sous antibiothérapie orale. Évolution rapidement favorable sous antibiothérapie orale d'emblée, sans nécessité d'oxygénothérapie.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Pneumopathie basale gauche</t>
         </is>
@@ -882,15 +922,20 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>UF Bloc opératoire</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>Mise en place d'une prothèse totale de hanche non cimentée, voie postéro-externe, sans incident peropératoire. Pertes sanguines estimées à 250mL.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Mise en place d'une prothèse totale de hanche non cimentée, voie postéro-externe, sans incident peropératoire. Pertes sanguines estimées à 250mL. Intervention réalisée sous rachianesthésie, durée opératoire de 55 minutes. Aucune transfusion peropératoire nécessaire. Suites immédiates simples.</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>prothèse totale de hanche</t>
         </is>
@@ -934,15 +979,20 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>UF Chirurgie orthopédique</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>Patient sortant avec appui partiel, traitement antalgique et anticoagulant préventif pendant 35 jours.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Patient sortant avec appui partiel, traitement antalgique et anticoagulant préventif pendant 35 jours. Consignes de rééducation transmises au centre de SSR, avec limitation de la flexion de hanche au-delà de 90° pendant 6 semaines.</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>anticoagulant préventif</t>
         </is>
@@ -986,15 +1036,20 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>UF Chirurgie orthopédique</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Coxarthrose évoluée symptomatique, indication de prothèse totale de hanche retenue.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Coxarthrose évoluée symptomatique, indication de prothèse totale de hanche retenue. Bilan pré-anesthésique programmé, absence de contre-indication à l'intervention à ce stade.</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>prothèse totale de hanche</t>
         </is>

--- a/data/documents.xlsx
+++ b/data/documents.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,27 +461,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>auteur</t>
+          <t>uf</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>uf</t>
+          <t>excerpt</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>excerpt</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
           <t>full_text</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>highlight</t>
         </is>
       </c>
     </row>
@@ -518,27 +508,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dr Martin</t>
+          <t>UF Cardiologie</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>UF Cardiologie</t>
+          <t>Patiente admise pour décompensation cardiaque globale sur cardiopathie ischémique connue, avec insuffisance rénale aiguë sur chronique stade IIIB. Évolution favorable sous traitement diurétique IV.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Patiente admise pour décompensation cardiaque globale sur cardiopathie ischémique connue, avec insuffisance rénale aiguë sur chronique stade IIIB. Évolution favorable sous traitement diurétique IV.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
           <t>Patiente admise pour décompensation cardiaque globale sur cardiopathie ischémique connue, avec insuffisance rénale aiguë sur chronique stade IIIB. Évolution favorable sous traitement diurétique IV. Le bilan biologique d'entrée retrouvait un NT-proBNP à 5400 ng/L et une créatininémie à 142 µmol/L. L'échocardiographie a confirmé une dysfonction ventriculaire gauche sévère (FEVG 30%). Traitement diurétique intraveineux avec surveillance stricte de la diurèse, permettant une amélioration clinique et biologique progressive. Sortie à domicile avec majoration du traitement de fond et mise en place d'une hospitalisation à domicile (HAD).</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>cardiopathie ischémique</t>
         </is>
       </c>
     </row>
@@ -575,27 +555,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dr Bianchi</t>
+          <t>UF Imagerie cardiaque</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>UF Imagerie cardiaque</t>
+          <t>FEVG estimée à 30%, hypokinésie globale. Pas d'épanchement péricardique. Valves sans anomalie significative.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FEVG estimée à 30%, hypokinésie globale. Pas d'épanchement péricardique. Valves sans anomalie significative.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
           <t>FEVG estimée à 30%, hypokinésie globale. Pas d'épanchement péricardique. Valves sans anomalie significative. Cinétique globale altérée de façon homogène, sans anomalie segmentaire focale évocatrice d'une séquelle territoriale univoque. Fonction diastolique non évaluable de façon fiable dans ce contexte.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>FEVG estimée à 30%</t>
         </is>
       </c>
     </row>
@@ -632,27 +602,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dr Martin</t>
+          <t>UF Cardiologie</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>UF Cardiologie</t>
+          <t>Poids stable à 68kg, auscultation pulmonaire libre. Poursuite du traitement, kaliémie basse à surveiller.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Poids stable à 68kg, auscultation pulmonaire libre. Poursuite du traitement, kaliémie basse à surveiller.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
           <t>Poids stable à 68kg, auscultation pulmonaire libre. Poursuite du traitement, kaliémie basse à surveiller. Le traitement bêta-bloquant et l'IEC ont été maintenus à dose stable. Surveillance rapprochée du ionogramme prévue en ville dans les 15 jours compte tenu de la kaliémie basse.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>kaliémie basse</t>
         </is>
       </c>
     </row>
@@ -689,27 +649,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dr Perrot</t>
+          <t>UF Cardiologie interventionnelle</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>UF Cardiologie interventionnelle</t>
+          <t>Sténose serrée de l'artère interventriculaire antérieure proximale, traitée par angioplastie et pose d'un stent actif.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sténose serrée de l'artère interventriculaire antérieure proximale, traitée par angioplastie et pose d'un stent actif.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
           <t>Sténose serrée de l'artère interventriculaire antérieure proximale, traitée par angioplastie et pose d'un stent actif. Angioplastie réalisée avec succès par voie radiale droite, sans complication au point de ponction. Double antiagrégation plaquettaire instaurée pour une durée de 12 mois.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>stent actif</t>
         </is>
       </c>
     </row>
@@ -746,27 +696,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dr Nguyen</t>
+          <t>UF Pneumologie</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>UF Pneumologie</t>
+          <t>Pneumopathie basale droite d'allure bactérienne, syndrome inflammatoire biologique marqué à l'entrée. Évolution favorable sous antibiothérapie.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Pneumopathie basale droite d'allure bactérienne, syndrome inflammatoire biologique marqué à l'entrée. Évolution favorable sous antibiothérapie.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
           <t>Pneumopathie basale droite d'allure bactérienne, syndrome inflammatoire biologique marqué à l'entrée. Évolution favorable sous antibiothérapie. Hémocultures négatives, antigénurie légionelle et pneumocoque négatives. Antibiothérapie probabiliste par amoxicilline-acide clavulanique avec relais oral à J5, bonne évolution clinique et biologique.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Pneumopathie basale droite</t>
         </is>
       </c>
     </row>
@@ -803,27 +743,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dr Roche</t>
+          <t>UF Imagerie</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>UF Imagerie</t>
+          <t>Foyer de condensation alvéolaire du lobe inférieur droit, sans épanchement pleural associé.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Foyer de condensation alvéolaire du lobe inférieur droit, sans épanchement pleural associé.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
           <t>Foyer de condensation alvéolaire du lobe inférieur droit, sans épanchement pleural associé. Contrôle radiologique de sortie non réalisé, à prévoir à distance si persistance de symptômes.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>foyer de condensation alvéolaire</t>
         </is>
       </c>
     </row>
@@ -860,27 +790,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dr Nguyen</t>
+          <t>UF Pneumologie</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>UF Pneumologie</t>
+          <t>Pneumopathie basale gauche, évolution favorable sous antibiothérapie orale.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Pneumopathie basale gauche, évolution favorable sous antibiothérapie orale.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
           <t>Pneumopathie basale gauche, évolution favorable sous antibiothérapie orale. Évolution rapidement favorable sous antibiothérapie orale d'emblée, sans nécessité d'oxygénothérapie.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Pneumopathie basale gauche</t>
         </is>
       </c>
     </row>
@@ -917,27 +837,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dr Lefevre</t>
+          <t>UF Bloc opératoire</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>UF Bloc opératoire</t>
+          <t>Mise en place d'une prothèse totale de hanche non cimentée, voie postéro-externe, sans incident peropératoire. Pertes sanguines estimées à 250mL.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Mise en place d'une prothèse totale de hanche non cimentée, voie postéro-externe, sans incident peropératoire. Pertes sanguines estimées à 250mL.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
           <t>Mise en place d'une prothèse totale de hanche non cimentée, voie postéro-externe, sans incident peropératoire. Pertes sanguines estimées à 250mL. Intervention réalisée sous rachianesthésie, durée opératoire de 55 minutes. Aucune transfusion peropératoire nécessaire. Suites immédiates simples.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>prothèse totale de hanche</t>
         </is>
       </c>
     </row>
@@ -974,27 +884,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dr Lefevre</t>
+          <t>UF Chirurgie orthopédique</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>UF Chirurgie orthopédique</t>
+          <t>Patient sortant avec appui partiel, traitement antalgique et anticoagulant préventif pendant 35 jours.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Patient sortant avec appui partiel, traitement antalgique et anticoagulant préventif pendant 35 jours.</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
           <t>Patient sortant avec appui partiel, traitement antalgique et anticoagulant préventif pendant 35 jours. Consignes de rééducation transmises au centre de SSR, avec limitation de la flexion de hanche au-delà de 90° pendant 6 semaines.</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>anticoagulant préventif</t>
         </is>
       </c>
     </row>
@@ -1031,27 +931,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dr Lefevre</t>
+          <t>UF Chirurgie orthopédique</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>UF Chirurgie orthopédique</t>
+          <t>Coxarthrose évoluée symptomatique, indication de prothèse totale de hanche retenue.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Coxarthrose évoluée symptomatique, indication de prothèse totale de hanche retenue.</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
           <t>Coxarthrose évoluée symptomatique, indication de prothèse totale de hanche retenue. Bilan pré-anesthésique programmé, absence de contre-indication à l'intervention à ce stade.</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>prothèse totale de hanche</t>
         </is>
       </c>
     </row>

--- a/data/documents.xlsx
+++ b/data/documents.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>sejour_key</t>
+          <t>id_sejour</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000098</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -666,47 +666,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REC-2024-00099</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>sej1</t>
-        </is>
-      </c>
+          <t>REC-2024-00187</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>doc1</t>
+          <t>hdoc1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Compte-rendu d'hospitalisation</t>
+          <t>Courrier de médecin traitant</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CRH — Séjour Pneumologie</t>
+          <t>Courrier d'adressage en cardiologie</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UF Pneumologie</t>
+          <t>UF Médecine générale</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pneumopathie basale droite d'allure bactérienne, syndrome inflammatoire biologique marqué à l'entrée. Évolution favorable sous antibiothérapie.</t>
+          <t>Patiente adressée pour bilan de dyspnée d'effort évoluant depuis plusieurs mois, dans un contexte de cardiopathie ischémique connue.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Pneumopathie basale droite d'allure bactérienne, syndrome inflammatoire biologique marqué à l'entrée. Évolution favorable sous antibiothérapie. Hémocultures négatives, antigénurie légionelle et pneumocoque négatives. Antibiothérapie probabiliste par amoxicilline-acide clavulanique avec relais oral à J5, bonne évolution clinique et biologique.</t>
+          <t>Patiente adressée pour bilan de dyspnée d'effort évoluant depuis plusieurs mois, dans un contexte de cardiopathie ischémique connue.
+Antécédents : hypertension artérielle, dyslipidémie.
+Traitement actuel : bêta-bloquant, statine.
+Merci de votre avis spécialisé.</t>
         </is>
       </c>
     </row>
@@ -718,42 +717,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000201</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>doc2</t>
+          <t>doc1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Compte-rendu de radiologie</t>
+          <t>Compte-rendu d'hospitalisation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Radiographie thoracique</t>
+          <t>CRH — Séjour Pneumologie</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>UF Imagerie</t>
+          <t>UF Pneumologie</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Foyer de condensation alvéolaire du lobe inférieur droit, sans épanchement pleural associé.</t>
+          <t>Pneumopathie basale droite d'allure bactérienne, syndrome inflammatoire biologique marqué à l'entrée. Évolution favorable sous antibiothérapie.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Foyer de condensation alvéolaire du lobe inférieur droit, sans épanchement pleural associé. Contrôle radiologique de sortie non réalisé, à prévoir à distance si persistance de symptômes.</t>
+          <t>Pneumopathie basale droite d'allure bactérienne, syndrome inflammatoire biologique marqué à l'entrée. Évolution favorable sous antibiothérapie. Hémocultures négatives, antigénurie légionelle et pneumocoque négatives. Antibiothérapie probabiliste par amoxicilline-acide clavulanique avec relais oral à J5, bonne évolution clinique et biologique.</t>
         </is>
       </c>
     </row>
@@ -765,54 +764,54 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000201</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>doc1</t>
+          <t>doc2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2023-03-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Compte-rendu d'hospitalisation</t>
+          <t>Compte-rendu de radiologie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CRH — Séjour Pneumologie (2023)</t>
+          <t>Radiographie thoracique</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UF Pneumologie</t>
+          <t>UF Imagerie</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pneumopathie basale gauche, évolution favorable sous antibiothérapie orale.</t>
+          <t>Foyer de condensation alvéolaire du lobe inférieur droit, sans épanchement pleural associé.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Pneumopathie basale gauche, évolution favorable sous antibiothérapie orale. Évolution rapidement favorable sous antibiothérapie orale d'emblée, sans nécessité d'oxygénothérapie.</t>
+          <t>Foyer de condensation alvéolaire du lobe inférieur droit, sans épanchement pleural associé. Contrôle radiologique de sortie non réalisé, à prévoir à distance si persistance de symptômes.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>REC-2024-00234</t>
+          <t>REC-2024-00099</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000077</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -822,32 +821,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2023-03-09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Compte-rendu opératoire</t>
+          <t>Compte-rendu d'hospitalisation</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Opératoire — PTH droite</t>
+          <t>CRH — Séjour Pneumologie (2023)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UF Bloc opératoire</t>
+          <t>UF Pneumologie</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Mise en place d'une prothèse totale de hanche non cimentée, voie postéro-externe, sans incident peropératoire. Pertes sanguines estimées à 250mL.</t>
+          <t>Pneumopathie basale gauche, évolution favorable sous antibiothérapie orale.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Mise en place d'une prothèse totale de hanche non cimentée, voie postéro-externe, sans incident peropératoire. Pertes sanguines estimées à 250mL. Intervention réalisée sous rachianesthésie, durée opératoire de 55 minutes. Aucune transfusion peropératoire nécessaire. Suites immédiates simples.</t>
+          <t>Pneumopathie basale gauche, évolution favorable sous antibiothérapie orale. Évolution rapidement favorable sous antibiothérapie orale d'emblée, sans nécessité d'oxygénothérapie.</t>
         </is>
       </c>
     </row>
@@ -859,42 +858,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000156</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>doc2</t>
+          <t>doc1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Compte-rendu de sortie</t>
+          <t>Compte-rendu opératoire</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lettre de sortie</t>
+          <t>CR Opératoire — PTH droite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>UF Chirurgie orthopédique</t>
+          <t>UF Bloc opératoire</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Patient sortant avec appui partiel, traitement antalgique et anticoagulant préventif pendant 35 jours.</t>
+          <t>Mise en place d'une prothèse totale de hanche non cimentée, voie postéro-externe, sans incident peropératoire. Pertes sanguines estimées à 250mL.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Patient sortant avec appui partiel, traitement antalgique et anticoagulant préventif pendant 35 jours. Consignes de rééducation transmises au centre de SSR, avec limitation de la flexion de hanche au-delà de 90° pendant 6 semaines.</t>
+          <t>Mise en place d'une prothèse totale de hanche non cimentée, voie postéro-externe, sans incident peropératoire. Pertes sanguines estimées à 250mL. Intervention réalisée sous rachianesthésie, durée opératoire de 55 minutes. Aucune transfusion peropératoire nécessaire. Suites immédiates simples.</t>
         </is>
       </c>
     </row>
@@ -906,40 +905,87 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000156</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>doc2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Compte-rendu de sortie</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lettre de sortie</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>UF Chirurgie orthopédique</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Patient sortant avec appui partiel, traitement antalgique et anticoagulant préventif pendant 35 jours.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Patient sortant avec appui partiel, traitement antalgique et anticoagulant préventif pendant 35 jours. Consignes de rééducation transmises au centre de SSR, avec limitation de la flexion de hanche au-delà de 90° pendant 6 semaines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>REC-2024-00234</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ID0000142</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>doc1</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>2024-05-15</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Compte-rendu de consultation</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>CR Consultation pré-opératoire</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>UF Chirurgie orthopédique</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Coxarthrose évoluée symptomatique, indication de prothèse totale de hanche retenue.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Coxarthrose évoluée symptomatique, indication de prothèse totale de hanche retenue. Bilan pré-anesthésique programmé, absence de contre-indication à l'intervention à ce stade.</t>
         </is>
